--- a/Proxies.xlsx
+++ b/Proxies.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nrossberg/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nrossberg/Documents/GitHub/Proxies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFC2FE4-7F8C-1048-AEB9-8B31AE5BD81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7323DA-A56E-9349-8AC3-187F01EEF809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="-28300" windowWidth="51200" windowHeight="28300" xr2:uid="{543621DB-B441-F74D-968F-679735AD534F}"/>
   </bookViews>
@@ -1103,7 +1103,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="1">
-        <v>3.375</v>
+        <v>3.1481481481481501</v>
       </c>
       <c r="D12" s="1">
         <v>71974</v>
@@ -1427,7 +1427,7 @@
         <v>35</v>
       </c>
       <c r="C24" s="1">
-        <v>3.1136363636363602</v>
+        <v>3.1388888888888902</v>
       </c>
       <c r="D24" s="1">
         <v>71974</v>
